--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-12-2025.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>£9.69</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/25mm-celotex-tb4025-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -678,7 +678,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>£11.10</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/30mm-celotex-tb4030-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -798,7 +798,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>£14.00</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/40mm-celotex-tb4040-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>£13.80</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/40mm-celotex-tb4040-pir-insulation-board-2400mm-x-1200mm-x-40mm</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -881,7 +881,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>£15.15</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/celotex-tb4040-high-performance-pir-insulation-2400mm-x-1200mm-x-40mm</t>
         </is>
       </c>
     </row>
@@ -918,14 +918,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/50mm-celotex-ga4050-pir-insulation-board-2400mm-x-1200mm</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>£14.55</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>£14.55</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>£14.68</t>
@@ -938,7 +938,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>£14.98</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/50mm-celotex-ga4050-pir-insulation-board-2400mm-x-1200mm-x-50mm</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>£18.16</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/60mm-celotex-ga4060-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1143,14 +1143,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/70mm-celotex-ga3070-2-4m-x-1-2m</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>£20.25</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>£20.25</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>£20.50</t>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>£20.24</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/70mm-celotex-ga4070-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 524 Server Error: &lt;none&gt; for url: https://edibleartistsnetwork.com/</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>£20.13</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/75mm-celotex-ga4075-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 522 Server Error: &lt;none&gt; for url: https://edibleartistsnetwork.com/</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>£23.35</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/80mm-celotex-ga4080-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>£25.40</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/90mm-celotex-ga4090-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>£25.10</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/100mm-celotex-ga4100-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1758,17 +1758,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/110mm-celotex-xr4110-pir-insulation-board-2400mm-x-1200mm</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>£32.15</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>£32.15</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£32.15</t>
+          <t>£31.93</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>£30.40</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/120mm-celotex-xr4120-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>£38.00</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/130mm-celotex-xr4130-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>£37.94</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/140mm-celotex-xr4140-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>£37.32</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/150mm-celotex-xr4150-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>£877.92</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/165mm-celotex-xr4165-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>£960.0</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/200mm-celotex-xr4200-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>£28.12</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/37-5mm-celotex-pl4025-insulated-plasterboard-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>£33.87</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/52-5mm-celotex-pl4040-insulated-plasterboard-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>£36.81</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/62-5mm-celotex-pl4050-insulated-plasterboard-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>£41.98</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/72-5mm-celotex-pl4060-insulated-plasterboard-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>£49.60</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/50mm-celotex-cavity-wall-insulation-board-1200mm-x-450mm-5-94m2-pack</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>£48.04</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/75mm-celotex-cavity-wall-insulation-board-1200mm-x-450mm-4-32m2-pack</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>£46.50</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/100mm-celotex-cavity-wall-insulation-board-1200mm-x-450mm-3-24m2-pack</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff61396a235
-	0x7ff6136c2630
-	0x7ff6134516dd
-	0x7ff6134aa27e
-	0x7ff6134aa58c
-	0x7ff6134fed77
-	0x7ff6134fbaba
-	0x7ff61349b0ed
-	0x7ff61349bf63
-	0x7ff613995d60
-	0x7ff61398fe8a
-	0x7ff6139b1005
-	0x7ff6136dd71e
-	0x7ff6136e4e1f
-	0x7ff6136cb7c4
-	0x7ff6136cb97f
-	0x7ff6136b18e8
+	0x7ff75bd1a235
+	0x7ff75ba72630
+	0x7ff75b8016dd
+	0x7ff75b85a27e
+	0x7ff75b85a58c
+	0x7ff75b8aed77
+	0x7ff75b8ababa
+	0x7ff75b84b0ed
+	0x7ff75b84bf63
+	0x7ff75bd45d60
+	0x7ff75bd3fe8a
+	0x7ff75bd61005
+	0x7ff75ba8d71e
+	0x7ff75ba94e1f
+	0x7ff75ba7b7c4
+	0x7ff75ba7b97f
+	0x7ff75ba618e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>£1248.0</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/90mm-celotex-thermaclass-cavity-wall-21-full-fill-insulation-board-t-g-1190mm-x-450mm-3-21m2-pack</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>£1328.0</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/115mm-celotex-thermaclass-cavity-wall-21-full-fill-insulation-board-t-g-1190mm-x-450mm-2-68m2-pack</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>£1280.0</t>
+          <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/140mm-celotex-thermaclass-cavity-wall-21-full-fill-insulation-board-t-g-1190mm-x-450mm-2-14m2-pack</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-12-2025.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/40mm-celotex-tb4040-pir-insulation-board-2400mm-x-1200mm-x-40mm</t>
+          <t>£13.80</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/celotex-tb4040-high-performance-pir-insulation-2400mm-x-1200mm-x-40mm</t>
+          <t>£15.15</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/50mm-celotex-ga4050-pir-insulation-board-2400mm-x-1200mm-x-50mm</t>
+          <t>£14.98</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/70mm-celotex-ga3070-2-4m-x-1-2m</t>
+          <t>£20.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 524 Server Error: &lt;none&gt; for url: https://edibleartistsnetwork.com/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 522 Server Error: &lt;none&gt; for url: https://edibleartistsnetwork.com/</t>
+          <t>Error: 524 Server Error: &lt;none&gt; for url: https://edibleartistsnetwork.com/</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
